--- a/reports/Nigerian_Ecommerce_Dashboard.xlsx
+++ b/reports/Nigerian_Ecommerce_Dashboard.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2025-07-12 19:40</t>
+          <t>2025-07-12 19:47</t>
         </is>
       </c>
     </row>
